--- a/exports/LODHA_full_report.xlsx
+++ b/exports/LODHA_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q69"/>
+  <dimension ref="A1:U69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>9.380000000000001</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44606.55208333334</v>
+        <v>44607.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>614.5</v>
+        <v>588.6</v>
       </c>
       <c r="I2" t="n">
         <v>612.9943054768486</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3</v>
+        <v>-3.93</v>
       </c>
       <c r="L2" t="n">
         <v>5.65</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>13.67</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44637.38541666666</v>
+        <v>44637.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>545</v>
+        <v>556</v>
       </c>
       <c r="I3" t="n">
         <v>555.5660803832407</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>30</v>
+        <v>30.16666666666667</v>
       </c>
       <c r="K3" t="n">
-        <v>7.41</v>
+        <v>5.54</v>
       </c>
       <c r="L3" t="n">
         <v>11.11</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>10.83</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44664.55208333334</v>
+        <v>44669.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>567</v>
+        <v>549.25</v>
       </c>
       <c r="I4" t="n">
         <v>561.5531507482341</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>27</v>
+        <v>31.83333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>1.98</v>
+        <v>-1.21</v>
       </c>
       <c r="L4" t="n">
         <v>5.19</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>9.25</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44712.55208333334</v>
+        <v>44713.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>481.6</v>
+        <v>502.15</v>
       </c>
       <c r="I5" t="n">
         <v>481.704651852753</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>44</v>
       </c>
       <c r="K5" t="n">
-        <v>12.32</v>
+        <v>8.58</v>
       </c>
       <c r="L5" t="n">
         <v>3.49</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>13.27</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44729.55208333334</v>
+        <v>44732.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>529.4</v>
+        <v>502.35</v>
       </c>
       <c r="I6" t="n">
         <v>503.0968243967217</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K6" t="n">
-        <v>5.43</v>
+        <v>0.04</v>
       </c>
       <c r="L6" t="n">
         <v>3.56</v>
@@ -783,7 +854,7 @@
         <v>2.2</v>
       </c>
       <c r="N6" t="n">
-        <v>4.72</v>
+        <v>5.55</v>
       </c>
       <c r="O6" t="n">
         <v>5.07</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>12.97</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44747.55208333334</v>
+        <v>44748.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>519</v>
+        <v>546.1</v>
       </c>
       <c r="I7" t="n">
         <v>544.6914554185424</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.31</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>8.779999999999999</v>
+        <v>8.99</v>
       </c>
       <c r="M7" t="n">
         <v>2.99</v>
       </c>
       <c r="N7" t="n">
-        <v>3.23</v>
+        <v>5.49</v>
       </c>
       <c r="O7" t="n">
         <v>-5.55</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>9.76</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44776.55208333334</v>
+        <v>44777.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>552.1</v>
+        <v>520.95</v>
       </c>
       <c r="I8" t="n">
         <v>546.2542248940847</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1</v>
+        <v>-4.61</v>
       </c>
       <c r="L8" t="n">
-        <v>4.05</v>
+        <v>7.07</v>
       </c>
       <c r="M8" t="n">
-        <v>1.06</v>
+        <v>2.46</v>
       </c>
       <c r="N8" t="n">
-        <v>3.61</v>
+        <v>6.09</v>
       </c>
       <c r="O8" t="n">
         <v>5.49</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>9.130000000000001</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44789.55208333334</v>
+        <v>44790.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>555.5</v>
+        <v>564.45</v>
       </c>
       <c r="I9" t="n">
         <v>561.4855339520585</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K9" t="n">
-        <v>-6.63</v>
+        <v>-8.35</v>
       </c>
       <c r="L9" t="n">
-        <v>7.4</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>0.85</v>
+        <v>1.26</v>
       </c>
       <c r="N9" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="O9" t="n">
         <v>-6.09</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>7.52</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44795.38541666666</v>
+        <v>44795.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>539.85</v>
+        <v>526.5</v>
       </c>
       <c r="I10" t="n">
         <v>530.1416460332666</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.36</v>
+        <v>-6.72</v>
       </c>
       <c r="L10" t="n">
-        <v>5.22</v>
+        <v>6.9</v>
       </c>
       <c r="M10" t="n">
         <v>0.05</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>8.66</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44840.55208333334</v>
+        <v>44841.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>492.35</v>
+        <v>504.75</v>
       </c>
       <c r="I11" t="n">
         <v>495.8811019521789</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>45</v>
+        <v>45.83333333333334</v>
       </c>
       <c r="K11" t="n">
-        <v>6.49</v>
+        <v>4.13</v>
       </c>
       <c r="L11" t="n">
         <v>6.34</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>8.460000000000001</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44869.55208333334</v>
+        <v>44872.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>476.05</v>
+        <v>466.5</v>
       </c>
       <c r="I12" t="n">
         <v>471.7139631042752</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K12" t="n">
-        <v>-5.69</v>
+        <v>-7.58</v>
       </c>
       <c r="L12" t="n">
-        <v>6.69</v>
+        <v>7.58</v>
       </c>
       <c r="M12" t="n">
         <v>1.41</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>7.16</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44880.38541666666</v>
+        <v>44880.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>476.15</v>
+        <v>496.5</v>
       </c>
       <c r="I13" t="n">
         <v>491.3322571297819</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.07</v>
+        <v>-6.43</v>
       </c>
       <c r="L13" t="n">
-        <v>4.17</v>
+        <v>6.5</v>
       </c>
       <c r="M13" t="n">
         <v>2.01</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>9.029999999999999</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44951.55208333334</v>
+        <v>44953.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>531.85</v>
+        <v>512.05</v>
       </c>
       <c r="I14" t="n">
         <v>515.4779304996368</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>71</v>
+        <v>72.83333333333333</v>
       </c>
       <c r="K14" t="n">
-        <v>7.12</v>
+        <v>3.13</v>
       </c>
       <c r="L14" t="n">
         <v>4.12</v>
@@ -1239,7 +1406,7 @@
         <v>1.6</v>
       </c>
       <c r="N14" t="n">
-        <v>5.17</v>
+        <v>5.22</v>
       </c>
       <c r="O14" t="n">
         <v>4.64</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>10.79</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44985.55208333334</v>
+        <v>44986.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>409.5</v>
+        <v>422.45</v>
       </c>
       <c r="I15" t="n">
         <v>411.2384339570262</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K15" t="n">
-        <v>20.03</v>
+        <v>17.5</v>
       </c>
       <c r="L15" t="n">
         <v>4.77</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>15.05</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44998.55208333334</v>
+        <v>44999.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>437.5</v>
+        <v>425.1</v>
       </c>
       <c r="I16" t="n">
         <v>433.7626082491147</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K16" t="n">
-        <v>3.56</v>
+        <v>0.63</v>
       </c>
       <c r="L16" t="n">
         <v>4.76</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>16.01</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45014.38541666666</v>
+        <v>45014.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>405</v>
+        <v>433.3</v>
       </c>
       <c r="I17" t="n">
         <v>432.1826710075981</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K17" t="n">
-        <v>4.73</v>
+        <v>-1.93</v>
       </c>
       <c r="L17" t="n">
         <v>7.74</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>13.98</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45118.38541666666</v>
+        <v>45118.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>667.95</v>
+        <v>663</v>
       </c>
       <c r="I18" t="n">
         <v>663.4443393048318</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>103.8333333333333</v>
+        <v>104</v>
       </c>
       <c r="K18" t="n">
-        <v>54.15</v>
+        <v>53.01</v>
       </c>
       <c r="L18" t="n">
         <v>6.92</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>136</v>
+        <v>137</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>9.1</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45128.55208333334</v>
+        <v>45131.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>704.95</v>
+        <v>731.8</v>
       </c>
       <c r="I19" t="n">
         <v>723.3391682255009</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>10</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K19" t="n">
-        <v>-6.33</v>
+        <v>-10.38</v>
       </c>
       <c r="L19" t="n">
-        <v>9.49</v>
+        <v>10.78</v>
       </c>
       <c r="M19" t="n">
         <v>0.6899999999999999</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>10.15</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45148.38541666666</v>
+        <v>45148.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>700.4</v>
+        <v>693</v>
       </c>
       <c r="I20" t="n">
         <v>700.076212427008</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K20" t="n">
-        <v>-4.29</v>
+        <v>-5.3</v>
       </c>
       <c r="L20" t="n">
-        <v>5.01</v>
+        <v>5.65</v>
       </c>
       <c r="M20" t="n">
         <v>3.94</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>7.56</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45170.55208333334</v>
+        <v>45173.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>680</v>
+        <v>701.9</v>
       </c>
       <c r="I21" t="n">
         <v>696.8038012123184</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>22</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="K21" t="n">
-        <v>1.88</v>
+        <v>-1.28</v>
       </c>
       <c r="L21" t="n">
         <v>5.34</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>8.880000000000001</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45191.55208333334</v>
+        <v>45194.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>739.4</v>
+        <v>733.1</v>
       </c>
       <c r="I22" t="n">
         <v>737.3323984372835</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K22" t="n">
-        <v>5.34</v>
+        <v>4.45</v>
       </c>
       <c r="L22" t="n">
         <v>3.39</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>9.84</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45208.55208333334</v>
+        <v>45209.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>782</v>
+        <v>805.8</v>
       </c>
       <c r="I23" t="n">
         <v>805.2582087411707</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K23" t="n">
-        <v>-6.67</v>
+        <v>-9.92</v>
       </c>
       <c r="L23" t="n">
         <v>12.4</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,25 +2075,25 @@
         <v>11.84</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45222.55208333334</v>
+        <v>45224.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>781</v>
+        <v>756.55</v>
       </c>
       <c r="I24" t="n">
         <v>761.8946830541281</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.08</v>
+        <v>-6.11</v>
       </c>
       <c r="L24" t="n">
-        <v>5.17</v>
+        <v>6.39</v>
       </c>
       <c r="M24" t="n">
-        <v>0.25</v>
+        <v>0.45</v>
       </c>
       <c r="N24" t="n">
         <v>3.7</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>11.15</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45231.55208333334</v>
+        <v>45232.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>797</v>
+        <v>837.7</v>
       </c>
       <c r="I25" t="n">
         <v>802.6151281458551</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K25" t="n">
-        <v>-5.35</v>
+        <v>-10.73</v>
       </c>
       <c r="L25" t="n">
-        <v>8.390000000000001</v>
+        <v>12.35</v>
       </c>
       <c r="M25" t="n">
         <v>1.55</v>
       </c>
       <c r="N25" t="n">
-        <v>3.83</v>
+        <v>6.27</v>
       </c>
       <c r="O25" t="n">
         <v>-3.28</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>11.31</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45311.55208333334</v>
+        <v>45314.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>1131.8</v>
+        <v>1060</v>
       </c>
       <c r="I26" t="n">
         <v>1098.105255204862</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>79.16666666666667</v>
+        <v>82</v>
       </c>
       <c r="K26" t="n">
-        <v>35.11</v>
+        <v>26.54</v>
       </c>
       <c r="L26" t="n">
         <v>4.06</v>
@@ -1923,7 +2234,7 @@
         <v>2.22</v>
       </c>
       <c r="N26" t="n">
-        <v>4.4</v>
+        <v>5.84</v>
       </c>
       <c r="O26" t="n">
         <v>6.27</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>111</v>
+        <v>112</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>14.48</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45349.38541666666</v>
+        <v>45349.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>1147.3</v>
+        <v>1150</v>
       </c>
       <c r="I27" t="n">
         <v>1149.861372254985</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K27" t="n">
-        <v>-8.24</v>
+        <v>-8.49</v>
       </c>
       <c r="L27" t="n">
         <v>13.88</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>8.140000000000001</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>1113.9</v>
+        <v>1032.8</v>
       </c>
       <c r="I28" t="n">
         <v>1099.458467553914</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K28" t="n">
-        <v>-3.14</v>
+        <v>-10.19</v>
       </c>
       <c r="L28" t="n">
-        <v>3.89</v>
+        <v>13.83</v>
       </c>
       <c r="M28" t="n">
         <v>0.02</v>
       </c>
       <c r="N28" t="n">
-        <v>5.52</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="O28" t="n">
         <v>3.23</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>19.38</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45383.55208333334</v>
+        <v>45384.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>1171.3</v>
+        <v>1185.65</v>
       </c>
       <c r="I29" t="n">
         <v>1180.949180021364</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K29" t="n">
-        <v>-13.41</v>
+        <v>-14.8</v>
       </c>
       <c r="L29" t="n">
-        <v>14.39</v>
+        <v>15.77</v>
       </c>
       <c r="M29" t="n">
         <v>1.28</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>9.390000000000001</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>1165</v>
+        <v>1118.5</v>
       </c>
       <c r="I30" t="n">
         <v>1156.20222522941</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.74</v>
+        <v>-5.66</v>
       </c>
       <c r="L30" t="n">
         <v>6.38</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>13.42</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45430.38541666666</v>
+        <v>45433.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>1207</v>
+        <v>1230.25</v>
       </c>
       <c r="I31" t="n">
         <v>1222.535095739512</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K31" t="n">
-        <v>-7.91</v>
+        <v>-9.99</v>
       </c>
       <c r="L31" t="n">
-        <v>8.82</v>
+        <v>11.73</v>
       </c>
       <c r="M31" t="n">
         <v>1.39</v>
       </c>
       <c r="N31" t="n">
-        <v>2.17</v>
+        <v>2.49</v>
       </c>
       <c r="O31" t="n">
         <v>-4.7</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>7.93</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45447.38541666666</v>
+        <v>45447.55208333334</v>
       </c>
       <c r="H32" t="n">
-        <v>1349.3</v>
+        <v>1309.8</v>
       </c>
       <c r="I32" t="n">
         <v>1314.717501192652</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K32" t="n">
-        <v>9.68</v>
+        <v>6.47</v>
       </c>
       <c r="L32" t="n">
         <v>2.22</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>14.27</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45450.55208333334</v>
+        <v>45453.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>1436.6</v>
+        <v>1479.6</v>
       </c>
       <c r="I33" t="n">
         <v>1461.517166630557</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>3</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K33" t="n">
-        <v>-9.68</v>
+        <v>-12.96</v>
       </c>
       <c r="L33" t="n">
-        <v>12.09</v>
+        <v>14.88</v>
       </c>
       <c r="M33" t="n">
         <v>2.74</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>14</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45469.38541666666</v>
+        <v>45469.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>1453.1</v>
+        <v>1439.9</v>
       </c>
       <c r="I34" t="n">
         <v>1442.739958257103</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K34" t="n">
-        <v>-1.79</v>
+        <v>-2.68</v>
       </c>
       <c r="L34" t="n">
         <v>3.33</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>10.05</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45513.55208333334</v>
+        <v>45516.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>1242</v>
+        <v>1298.5</v>
       </c>
       <c r="I35" t="n">
         <v>1292.452999341947</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>44</v>
+        <v>46.83333333333334</v>
       </c>
       <c r="K35" t="n">
-        <v>13.74</v>
+        <v>9.82</v>
       </c>
       <c r="L35" t="n">
         <v>10.77</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>11.74</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45526.55208333334</v>
+        <v>45527.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>1218.7</v>
+        <v>1169.45</v>
       </c>
       <c r="I36" t="n">
         <v>1200.26375980578</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K36" t="n">
-        <v>-6.15</v>
+        <v>-9.94</v>
       </c>
       <c r="L36" t="n">
-        <v>6.42</v>
+        <v>10.22</v>
       </c>
       <c r="M36" t="n">
         <v>0.58</v>
       </c>
       <c r="N36" t="n">
-        <v>2.19</v>
+        <v>4.57</v>
       </c>
       <c r="O36" t="n">
         <v>4.43</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>10.04</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45533.38541666666</v>
+        <v>45533.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>1243.85</v>
+        <v>1254</v>
       </c>
       <c r="I37" t="n">
         <v>1252.17575443654</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K37" t="n">
-        <v>-6.36</v>
+        <v>-7.23</v>
       </c>
       <c r="L37" t="n">
         <v>10.18</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>7.95</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45562.38541666666</v>
+        <v>45562.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>1332.55</v>
+        <v>1280.85</v>
       </c>
       <c r="I38" t="n">
         <v>1307.654384680276</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>28.83333333333333</v>
+        <v>29</v>
       </c>
       <c r="K38" t="n">
-        <v>6.26</v>
+        <v>2.14</v>
       </c>
       <c r="L38" t="n">
         <v>7.05</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>12.8</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45593.55208333334</v>
+        <v>45594.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>1104.95</v>
+        <v>1164.85</v>
       </c>
       <c r="I39" t="n">
         <v>1156.217303297859</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>31</v>
+        <v>31.83333333333333</v>
       </c>
       <c r="K39" t="n">
-        <v>13.73</v>
+        <v>9.06</v>
       </c>
       <c r="L39" t="n">
         <v>4.74</v>
@@ -2664,7 +3131,7 @@
         <v>3.73</v>
       </c>
       <c r="N39" t="n">
-        <v>3.49</v>
+        <v>7.1</v>
       </c>
       <c r="O39" t="n">
         <v>-7.32</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>13.08</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45656.55208333334</v>
+        <v>45657.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>1400</v>
+        <v>1361.15</v>
       </c>
       <c r="I40" t="n">
         <v>1389.222187199085</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>62.16666666666666</v>
+        <v>63</v>
       </c>
       <c r="K40" t="n">
-        <v>20.19</v>
+        <v>16.85</v>
       </c>
       <c r="L40" t="n">
         <v>5.79</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>9.58</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45687.55208333334</v>
+        <v>45688.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>1166</v>
+        <v>1210.85</v>
       </c>
       <c r="I41" t="n">
         <v>1190.127889421922</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K41" t="n">
-        <v>14.34</v>
+        <v>11.04</v>
       </c>
       <c r="L41" t="n">
         <v>6.38</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>10.78</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45698.55208333334</v>
+        <v>45699.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>1178.65</v>
+        <v>1151</v>
       </c>
       <c r="I42" t="n">
         <v>1174.542757583669</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K42" t="n">
-        <v>-2.66</v>
+        <v>-4.94</v>
       </c>
       <c r="L42" t="n">
-        <v>4.35</v>
+        <v>5.22</v>
       </c>
       <c r="M42" t="n">
         <v>1.15</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>10.84</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45734.55208333334</v>
+        <v>45735.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>1112.1</v>
+        <v>1160.6</v>
       </c>
       <c r="I43" t="n">
         <v>1153.435981506395</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K43" t="n">
-        <v>3.38</v>
+        <v>-0.83</v>
       </c>
       <c r="L43" t="n">
         <v>6.2</v>
@@ -2892,7 +3407,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="N43" t="n">
-        <v>5.39</v>
+        <v>6.1</v>
       </c>
       <c r="O43" t="n">
         <v>-0.9</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>10.49</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>1187</v>
+        <v>1116.95</v>
       </c>
       <c r="I44" t="n">
         <v>1126.343174599128</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K44" t="n">
-        <v>2.27</v>
+        <v>-3.76</v>
       </c>
       <c r="L44" t="n">
-        <v>4.06</v>
+        <v>6.56</v>
       </c>
       <c r="M44" t="n">
-        <v>0.77</v>
+        <v>5.94</v>
       </c>
       <c r="N44" t="n">
-        <v>3.94</v>
+        <v>5.65</v>
       </c>
       <c r="O44" t="n">
         <v>6.1</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>11.4</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45762.55208333334</v>
+        <v>45763.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>1215.9</v>
+        <v>1243.6</v>
       </c>
       <c r="I45" t="n">
         <v>1224.46046364998</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K45" t="n">
-        <v>-8.859999999999999</v>
+        <v>-11.34</v>
       </c>
       <c r="L45" t="n">
-        <v>8.949999999999999</v>
+        <v>12.35</v>
       </c>
       <c r="M45" t="n">
         <v>3.21</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,25 +3593,25 @@
         <v>9.539999999999999</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45785.55208333334</v>
+        <v>45786.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>1276.6</v>
+        <v>1230</v>
       </c>
       <c r="I46" t="n">
         <v>1254.941592809867</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K46" t="n">
-        <v>2.65</v>
+        <v>-1.09</v>
       </c>
       <c r="L46" t="n">
         <v>1.5</v>
       </c>
       <c r="M46" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="N46" t="n">
         <v>3.15</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>10.25</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45791.55208333334</v>
+        <v>45792.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>1313.1</v>
+        <v>1371.3</v>
       </c>
       <c r="I47" t="n">
         <v>1336.432942587731</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K47" t="n">
-        <v>-6.76</v>
+        <v>-11.49</v>
       </c>
       <c r="L47" t="n">
-        <v>7.97</v>
+        <v>11.71</v>
       </c>
       <c r="M47" t="n">
         <v>4.84</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,25 +3731,25 @@
         <v>11.09</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45820.55208333334</v>
+        <v>45821.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>1445.2</v>
+        <v>1432.2</v>
       </c>
       <c r="I48" t="n">
         <v>1433.630851782372</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K48" t="n">
-        <v>5.39</v>
+        <v>4.44</v>
       </c>
       <c r="L48" t="n">
         <v>4.76</v>
       </c>
       <c r="M48" t="n">
-        <v>0.6</v>
+        <v>0.83</v>
       </c>
       <c r="N48" t="n">
         <v>2.71</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>5.42</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45853.55208333334</v>
+        <v>45854.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>1434</v>
+        <v>1444.4</v>
       </c>
       <c r="I49" t="n">
         <v>1440.077353473521</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.13</v>
+        <v>-0.85</v>
       </c>
       <c r="L49" t="n">
         <v>5.42</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>4.61</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45860.55208333334</v>
+        <v>45861.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>1444</v>
+        <v>1349.2</v>
       </c>
       <c r="I50" t="n">
         <v>1392.556528828523</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.03</v>
+        <v>-6.59</v>
       </c>
       <c r="L50" t="n">
-        <v>0.93</v>
+        <v>6.78</v>
       </c>
       <c r="M50" t="n">
-        <v>0.1</v>
+        <v>3.05</v>
       </c>
       <c r="N50" t="n">
-        <v>0.17</v>
+        <v>7.76</v>
       </c>
       <c r="O50" t="n">
         <v>0.29</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>7.6</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45889.38541666666</v>
+        <v>45889.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>1283.5</v>
+        <v>1298</v>
       </c>
       <c r="I51" t="n">
         <v>1283.715896320317</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>28</v>
+        <v>28.16666666666667</v>
       </c>
       <c r="K51" t="n">
-        <v>4.87</v>
+        <v>3.79</v>
       </c>
       <c r="L51" t="n">
         <v>4.06</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>5.38</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45894.55208333334</v>
+        <v>45895.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>1264.5</v>
+        <v>1241.3</v>
       </c>
       <c r="I52" t="n">
         <v>1248.01537017002</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K52" t="n">
-        <v>-2.58</v>
+        <v>-4.37</v>
       </c>
       <c r="L52" t="n">
-        <v>2.93</v>
+        <v>4.82</v>
       </c>
       <c r="M52" t="n">
         <v>-0</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>6.18</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45919.55208333334</v>
+        <v>45922.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>1217.2</v>
+        <v>1228</v>
       </c>
       <c r="I53" t="n">
         <v>1223.589229383099</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K53" t="n">
-        <v>1.94</v>
+        <v>1.07</v>
       </c>
       <c r="L53" t="n">
         <v>2.22</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>5.17</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45924.55208333334</v>
+        <v>45925.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>1178.2</v>
+        <v>1155.7</v>
       </c>
       <c r="I54" t="n">
         <v>1166.635754043215</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K54" t="n">
-        <v>-4.06</v>
+        <v>-5.89</v>
       </c>
       <c r="L54" t="n">
-        <v>4.32</v>
+        <v>6.15</v>
       </c>
       <c r="M54" t="n">
         <v>-0</v>
       </c>
       <c r="N54" t="n">
-        <v>2.22</v>
+        <v>2.48</v>
       </c>
       <c r="O54" t="n">
         <v>-0.42</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>5.85</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45944.55208333334</v>
+        <v>45945.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>1138.6</v>
+        <v>1177.7</v>
       </c>
       <c r="I55" t="n">
         <v>1166.421458124208</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K55" t="n">
-        <v>1.48</v>
+        <v>-1.9</v>
       </c>
       <c r="L55" t="n">
-        <v>2.22</v>
+        <v>2.74</v>
       </c>
       <c r="M55" t="n">
         <v>0.87</v>
       </c>
       <c r="N55" t="n">
-        <v>2.41</v>
+        <v>3</v>
       </c>
       <c r="O55" t="n">
         <v>-2.48</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>6.59</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45981.55208333334</v>
+        <v>45982.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>1200.1</v>
+        <v>1174.3</v>
       </c>
       <c r="I56" t="n">
         <v>1178.382746401468</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K56" t="n">
-        <v>1.9</v>
+        <v>-0.29</v>
       </c>
       <c r="L56" t="n">
         <v>2.84</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>5.52</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46024.55208333334</v>
+        <v>46027.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>1087</v>
+        <v>1118.8</v>
       </c>
       <c r="I57" t="n">
         <v>1098.561564508501</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K57" t="n">
-        <v>7.43</v>
+        <v>4.73</v>
       </c>
       <c r="L57" t="n">
         <v>2.36</v>
@@ -3690,7 +4373,7 @@
         <v>4.5</v>
       </c>
       <c r="N57" t="n">
-        <v>2.14</v>
+        <v>3.22</v>
       </c>
       <c r="O57" t="n">
         <v>-2.09</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>5.17</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46030.55208333334</v>
+        <v>46031.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>1086.9</v>
+        <v>1063.5</v>
       </c>
       <c r="I58" t="n">
         <v>1076.046147137291</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K58" t="n">
-        <v>-2.85</v>
+        <v>-4.94</v>
       </c>
       <c r="L58" t="n">
-        <v>3.01</v>
+        <v>5.77</v>
       </c>
       <c r="M58" t="n">
-        <v>0.03</v>
+        <v>0.45</v>
       </c>
       <c r="N58" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="O58" t="n">
         <v>3.22</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>6.06</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46055.55208333334</v>
+        <v>46056.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>963.5</v>
+        <v>1030.55</v>
       </c>
       <c r="I59" t="n">
         <v>971.1167096829155</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K59" t="n">
-        <v>9.4</v>
+        <v>3.1</v>
       </c>
       <c r="L59" t="n">
         <v>2.34</v>
       </c>
       <c r="M59" t="n">
-        <v>1.16</v>
+        <v>2.18</v>
       </c>
       <c r="N59" t="n">
-        <v>4.55</v>
+        <v>7.33</v>
       </c>
       <c r="O59" t="n">
         <v>-2.11</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>12.79</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46076.55208333334</v>
+        <v>46077.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>1075.45</v>
+        <v>1041.5</v>
       </c>
       <c r="I60" t="n">
         <v>1047.639524587861</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K60" t="n">
-        <v>4.36</v>
+        <v>1.06</v>
       </c>
       <c r="L60" t="n">
         <v>4.47</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>8.06</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>717.5</v>
+        <v>774.35</v>
       </c>
       <c r="I61" t="n">
         <v>733.9188616337807</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K61" t="n">
-        <v>31.11</v>
+        <v>25.65</v>
       </c>
       <c r="L61" t="n">
         <v>3.55</v>
       </c>
       <c r="M61" t="n">
-        <v>2.98</v>
+        <v>5.2</v>
       </c>
       <c r="N61" t="n">
-        <v>2.39</v>
+        <v>8.75</v>
       </c>
       <c r="O61" t="n">
         <v>-1.9</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>10.79</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46154.38541666666</v>
+        <v>46154.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>907.35</v>
+        <v>884</v>
       </c>
       <c r="I62" t="n">
         <v>900.8891060161754</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>34</v>
+        <v>34.16666666666666</v>
       </c>
       <c r="K62" t="n">
-        <v>17.18</v>
+        <v>14.16</v>
       </c>
       <c r="L62" t="n">
         <v>2.62</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>9.01</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46168.55208333334</v>
+        <v>46169.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>904.2</v>
+        <v>919.25</v>
       </c>
       <c r="I63" t="n">
         <v>907.3849373886542</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K63" t="n">
-        <v>-2.29</v>
+        <v>-3.99</v>
       </c>
       <c r="L63" t="n">
-        <v>3.22</v>
+        <v>5.77</v>
       </c>
       <c r="M63" t="n">
         <v>1.85</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>6.2</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46175.55208333334</v>
+        <v>46176.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>905</v>
+        <v>875</v>
       </c>
       <c r="I64" t="n">
         <v>884.1025889614469</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K64" t="n">
-        <v>-1.55</v>
+        <v>-4.81</v>
       </c>
       <c r="L64" t="n">
         <v>5.25</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,25 +4904,25 @@
         <v>9.69</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>898.9</v>
+        <v>935.75</v>
       </c>
       <c r="I65" t="n">
         <v>924.7750126501943</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K65" t="n">
-        <v>-2.73</v>
+        <v>-6.94</v>
       </c>
       <c r="L65" t="n">
-        <v>3.89</v>
+        <v>7.77</v>
       </c>
       <c r="M65" t="n">
-        <v>1.96</v>
+        <v>2.29</v>
       </c>
       <c r="N65" t="n">
         <v>3.56</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,25 +4973,25 @@
         <v>8.289999999999999</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46265.55208333334</v>
+        <v>46266.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>1239.9</v>
+        <v>1206.1</v>
       </c>
       <c r="I66" t="n">
         <v>1218.529648091931</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>77.16666666666667</v>
+        <v>78</v>
       </c>
       <c r="K66" t="n">
-        <v>32.5</v>
+        <v>28.89</v>
       </c>
       <c r="L66" t="n">
         <v>3.8</v>
       </c>
       <c r="M66" t="n">
-        <v>1.6</v>
+        <v>2.02</v>
       </c>
       <c r="N66" t="n">
         <v>4.31</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>4</v>
+      </c>
+      <c r="U66" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>6.55</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46287.55208333334</v>
+        <v>46288.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>1143</v>
+        <v>1163.3</v>
       </c>
       <c r="I67" t="n">
         <v>1159.687849322647</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K67" t="n">
-        <v>5.23</v>
+        <v>3.55</v>
       </c>
       <c r="L67" t="n">
         <v>3.18</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>6.71</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46295.55208333334</v>
+        <v>46296.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>1122.5</v>
+        <v>1098.1</v>
       </c>
       <c r="I68" t="n">
         <v>1102.322482797182</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K68" t="n">
-        <v>-3.51</v>
+        <v>-5.6</v>
       </c>
       <c r="L68" t="n">
-        <v>6.15</v>
+        <v>6.56</v>
       </c>
       <c r="M68" t="n">
         <v>1.47</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4377,6 +5204,12 @@
       <c r="Q69" t="n">
         <v>34</v>
       </c>
+      <c r="R69" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6479,7 +7312,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.6</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="6">
@@ -6489,7 +7322,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -6499,7 +7332,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>103.8</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8">
@@ -6509,7 +7342,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -6519,7 +7352,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32.2</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
@@ -6529,7 +7362,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>43.5</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="11">
@@ -6539,7 +7372,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12">
@@ -6549,7 +7382,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
@@ -6559,7 +7392,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>70.09999999999999</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="14">
@@ -6569,7 +7402,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.46</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="15">
@@ -6579,7 +7412,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.97</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="16">
@@ -6589,7 +7422,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.9</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="17">
@@ -6599,7 +7432,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>54.15</v>
+        <v>53.01</v>
       </c>
     </row>
     <row r="18">
@@ -6609,7 +7442,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>53.7</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="19">
@@ -6619,7 +7452,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.61</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="20">
@@ -6629,7 +7462,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.77</v>
+        <v>5.79</v>
       </c>
     </row>
     <row r="21">
@@ -6639,7 +7472,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14.39</v>
+        <v>15.77</v>
       </c>
     </row>
     <row r="22">
@@ -6649,7 +7482,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23">
@@ -6659,7 +7492,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
@@ -6669,7 +7502,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="25">
@@ -6679,7 +7512,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.01</v>
+        <v>5.94</v>
       </c>
     </row>
     <row r="26">
@@ -6689,7 +7522,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.62</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="27">
@@ -6709,7 +7542,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29">
